--- a/artfynd/A 24321-2022 artfynd.xlsx
+++ b/artfynd/A 24321-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24321-2022 artfynd.xlsx
+++ b/artfynd/A 24321-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105157144</v>
+        <v>105157142</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604612.9517859267</v>
+        <v>604605</v>
       </c>
       <c r="R2" t="n">
-        <v>7038563.191614258</v>
+        <v>7038634</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,14 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105157140</v>
+        <v>105157143</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604689.94865178</v>
+        <v>604586</v>
       </c>
       <c r="R3" t="n">
-        <v>7038511.116050546</v>
+        <v>7038615</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,24 +849,9 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,19 +882,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105157143</v>
+        <v>105157144</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604586.6012450007</v>
+        <v>604613</v>
       </c>
       <c r="R4" t="n">
-        <v>7038615.13744681</v>
+        <v>7038563</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +950,9 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,6 +976,317 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105157145</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>604635</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7038502</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102095060</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>604719</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7038497</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105157140</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>604690</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7038511</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 24321-2022 artfynd.xlsx
+++ b/artfynd/A 24321-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157143</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157144</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157145</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102095060</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,8 +1321,21 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157140</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>